--- a/030-試験/総合試験/033-総合試験計画書兼結果書.xlsx
+++ b/030-試験/総合試験/033-総合試験計画書兼結果書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\030-試験\総合試験\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8097FC45-1F93-4152-BD20-E2EFBD9E2996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5CB7DC-E5E4-4F97-89FE-B52166B1217D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8C3D73FB-0868-4F7E-BB2A-47AEE9ECD866}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="商品検索結果画面_カテゴリー検索" sheetId="8" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">総合試験_商品検索画面!$A$1:$BV$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">総合試験_商品検索画面!$A$1:$BV$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="77">
   <si>
     <t>システムID</t>
     <phoneticPr fontId="4"/>
@@ -212,13 +212,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>・パスワードがマスク表示される</t>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>3.【ログイン】を押下し、メイン画面に遷移する</t>
     <rPh sb="9" eb="11">
       <t>オウカ</t>
@@ -233,14 +226,6 @@
   </si>
   <si>
     <t>要件定義書 項番：17</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>要件定義書 項番：</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>113,114,116,118,17</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -331,20 +316,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>検索時に該当商品がないこと</t>
-    <rPh sb="0" eb="3">
-      <t>ケンサクジ</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>ガイトウショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>7.9,13,14,27,35</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>1. メイン画面でカテゴリ「帽子」を指定</t>
     <rPh sb="6" eb="8">
       <t>ガメン</t>
@@ -382,29 +353,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>・ログイン画面でパスワードが入力される</t>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>・ログイン画面で会員IDが入力される</t>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カイイン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>ログイン画面に遷移</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -423,16 +371,6 @@
       <t>ガメン</t>
     </rPh>
     <rPh sb="14" eb="16">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>・メイン画面に遷移</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
@@ -579,48 +517,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>・メイン画面に遷移</t>
-    <rPh sb="7" eb="9">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>検索してページング遷移すること</t>
-    <rPh sb="0" eb="2">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>1. 【検索】を押下し、商品検索結果画面に遷移</t>
-    <rPh sb="4" eb="6">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>・商品が10件表示される</t>
     <rPh sb="1" eb="3">
       <t>ショウヒン</t>
@@ -695,56 +591,11 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>2.【次へ】を押下し、次ページに遷移する</t>
-    <rPh sb="3" eb="4">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>3.【前へ】を押下し、前ページに遷移する</t>
-    <rPh sb="3" eb="4">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>・前ページに遷移</t>
     <rPh sb="1" eb="2">
       <t>マエ</t>
     </rPh>
     <rPh sb="6" eb="8">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>4.【2】を押下し、2ページ目に遷移する</t>
-    <rPh sb="6" eb="8">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
@@ -770,10 +621,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>20,28,30,32,33,34</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>※１</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -784,6 +631,113 @@
     </rPh>
     <rPh sb="14" eb="15">
       <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>要件定義書 項番：18</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>30,32,33,34,35</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>7.9,13,14,20,27,28,</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>4. 【検索】を押下し、商品検索結果画面に遷移</t>
+    <rPh sb="4" eb="6">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>5.【次へ】を押下し、次ページに遷移する</t>
+    <rPh sb="3" eb="4">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>6.【前へ】を押下し、前ページに遷移する</t>
+    <rPh sb="3" eb="4">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>7.【2】を押下し、2ページ目に遷移する</t>
+    <rPh sb="6" eb="8">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・メイン画面に遷移</t>
+  </si>
+  <si>
+    <t>検索時、商品一覧画面が正しく動作すること</t>
+    <rPh sb="0" eb="3">
+      <t>ケンサクジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ドウサ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1188,7 +1142,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1344,15 +1298,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
@@ -1368,15 +1313,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1419,6 +1355,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1518,6 +1456,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2188,10 +2127,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF276156-8A96-4E3A-9C62-608C05A10956}">
-  <dimension ref="A1:CA366"/>
+  <dimension ref="A1:CA367"/>
   <sheetFormatPr defaultColWidth="2.6640625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="4" width="1.6640625" style="1" customWidth="1"/>
     <col min="5" max="18" width="3" style="1" customWidth="1"/>
     <col min="19" max="34" width="2.6640625" style="1" customWidth="1"/>
     <col min="35" max="49" width="2.88671875" style="1" customWidth="1"/>
@@ -2200,181 +2139,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:74" customFormat="1" ht="14.4" customHeight="1" thickTop="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="90" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="100"/>
+      <c r="U1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="92"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="122"/>
-      <c r="AI1" s="90" t="s">
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="86"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
+      <c r="AC1" s="117"/>
+      <c r="AD1" s="117"/>
+      <c r="AE1" s="117"/>
+      <c r="AF1" s="117"/>
+      <c r="AG1" s="117"/>
+      <c r="AH1" s="118"/>
+      <c r="AI1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="AJ1" s="91"/>
-      <c r="AK1" s="91"/>
-      <c r="AL1" s="92"/>
-      <c r="AM1" s="114">
+      <c r="AJ1" s="85"/>
+      <c r="AK1" s="85"/>
+      <c r="AL1" s="86"/>
+      <c r="AM1" s="110">
         <v>45574</v>
       </c>
-      <c r="AN1" s="115"/>
-      <c r="AO1" s="115"/>
-      <c r="AP1" s="115"/>
-      <c r="AQ1" s="115"/>
-      <c r="AR1" s="115"/>
-      <c r="AS1" s="115"/>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="116"/>
-      <c r="AW1" s="78" t="s">
+      <c r="AN1" s="111"/>
+      <c r="AO1" s="111"/>
+      <c r="AP1" s="111"/>
+      <c r="AQ1" s="111"/>
+      <c r="AR1" s="111"/>
+      <c r="AS1" s="111"/>
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="112"/>
+      <c r="AW1" s="72" t="s">
         <v>2</v>
       </c>
       <c r="AX1" s="61"/>
-      <c r="AY1" s="123"/>
-      <c r="AZ1" s="124"/>
-      <c r="BA1" s="124"/>
-      <c r="BB1" s="125"/>
+      <c r="AY1" s="119"/>
+      <c r="AZ1" s="120"/>
+      <c r="BA1" s="120"/>
+      <c r="BB1" s="121"/>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
-      <c r="BK1" s="88"/>
-      <c r="BL1" s="88"/>
-      <c r="BM1" s="88"/>
-      <c r="BN1" s="88"/>
-      <c r="BO1" s="88"/>
-      <c r="BP1" s="88"/>
-      <c r="BQ1" s="88"/>
-      <c r="BR1" s="88"/>
-      <c r="BS1" s="88"/>
-      <c r="BT1" s="88"/>
-      <c r="BU1" s="88"/>
+      <c r="BK1" s="82"/>
+      <c r="BL1" s="82"/>
+      <c r="BM1" s="82"/>
+      <c r="BN1" s="82"/>
+      <c r="BO1" s="82"/>
+      <c r="BP1" s="82"/>
+      <c r="BQ1" s="82"/>
+      <c r="BR1" s="82"/>
+      <c r="BS1" s="82"/>
+      <c r="BT1" s="82"/>
+      <c r="BU1" s="82"/>
     </row>
     <row r="2" spans="1:74" customFormat="1" ht="14.4" customHeight="1" thickBot="1">
-      <c r="A2" s="105"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="106"/>
-      <c r="T2" s="107"/>
-      <c r="U2" s="93" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="102"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="102"/>
+      <c r="R2" s="102"/>
+      <c r="S2" s="102"/>
+      <c r="T2" s="103"/>
+      <c r="U2" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="94"/>
-      <c r="W2" s="94"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="117" t="s">
+      <c r="V2" s="88"/>
+      <c r="W2" s="88"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="118"/>
-      <c r="AA2" s="118"/>
-      <c r="AB2" s="118"/>
-      <c r="AC2" s="118"/>
-      <c r="AD2" s="118"/>
-      <c r="AE2" s="118"/>
-      <c r="AF2" s="118"/>
-      <c r="AG2" s="118"/>
-      <c r="AH2" s="119"/>
-      <c r="AI2" s="93" t="s">
+      <c r="Z2" s="114"/>
+      <c r="AA2" s="114"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
+      <c r="AE2" s="114"/>
+      <c r="AF2" s="114"/>
+      <c r="AG2" s="114"/>
+      <c r="AH2" s="115"/>
+      <c r="AI2" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="AJ2" s="94"/>
-      <c r="AK2" s="94"/>
-      <c r="AL2" s="95"/>
-      <c r="AM2" s="117" t="s">
+      <c r="AJ2" s="88"/>
+      <c r="AK2" s="88"/>
+      <c r="AL2" s="89"/>
+      <c r="AM2" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="AN2" s="118"/>
-      <c r="AO2" s="118"/>
-      <c r="AP2" s="118"/>
-      <c r="AQ2" s="118"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="118"/>
-      <c r="AT2" s="118"/>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="119"/>
-      <c r="AW2" s="79"/>
+      <c r="AN2" s="114"/>
+      <c r="AO2" s="114"/>
+      <c r="AP2" s="114"/>
+      <c r="AQ2" s="114"/>
+      <c r="AR2" s="114"/>
+      <c r="AS2" s="114"/>
+      <c r="AT2" s="114"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="115"/>
+      <c r="AW2" s="73"/>
       <c r="AX2" s="62"/>
-      <c r="AY2" s="126"/>
-      <c r="AZ2" s="127"/>
-      <c r="BA2" s="127"/>
-      <c r="BB2" s="128"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="123"/>
+      <c r="BA2" s="123"/>
+      <c r="BB2" s="124"/>
       <c r="BC2" s="1"/>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
-      <c r="BK2" s="89"/>
-      <c r="BL2" s="89"/>
-      <c r="BM2" s="89"/>
-      <c r="BN2" s="89"/>
-      <c r="BO2" s="89"/>
-      <c r="BP2" s="89"/>
-      <c r="BQ2" s="89"/>
-      <c r="BR2" s="89"/>
-      <c r="BS2" s="89"/>
-      <c r="BT2" s="89"/>
-      <c r="BU2" s="89"/>
+      <c r="BK2" s="83"/>
+      <c r="BL2" s="83"/>
+      <c r="BM2" s="83"/>
+      <c r="BN2" s="83"/>
+      <c r="BO2" s="83"/>
+      <c r="BP2" s="83"/>
+      <c r="BQ2" s="83"/>
+      <c r="BR2" s="83"/>
+      <c r="BS2" s="83"/>
+      <c r="BT2" s="83"/>
+      <c r="BU2" s="83"/>
     </row>
     <row r="3" spans="1:74" ht="14.4" customHeight="1" thickTop="1">
-      <c r="BK3" s="73"/>
-      <c r="BL3" s="73"/>
-      <c r="BM3" s="73"/>
-      <c r="BN3" s="73"/>
-      <c r="BO3" s="73"/>
-      <c r="BP3" s="73"/>
-      <c r="BQ3" s="73"/>
-      <c r="BR3" s="73"/>
-      <c r="BS3" s="73"/>
-      <c r="BT3" s="73"/>
-      <c r="BU3" s="73"/>
+      <c r="BK3" s="70"/>
+      <c r="BL3" s="70"/>
+      <c r="BM3" s="70"/>
+      <c r="BN3" s="70"/>
+      <c r="BO3" s="70"/>
+      <c r="BP3" s="70"/>
+      <c r="BQ3" s="70"/>
+      <c r="BR3" s="70"/>
+      <c r="BS3" s="70"/>
+      <c r="BT3" s="70"/>
+      <c r="BU3" s="70"/>
     </row>
     <row r="4" spans="1:74" ht="14.4" customHeight="1">
-      <c r="A4" s="80" t="s">
-        <v>82</v>
+      <c r="A4" s="74" t="s">
+        <v>67</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2435,172 +2374,172 @@
       <c r="BF4" s="2"/>
     </row>
     <row r="5" spans="1:74" s="4" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="108" t="s">
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="108" t="s">
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="110"/>
-      <c r="S5" s="108" t="s">
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+      <c r="R5" s="106"/>
+      <c r="S5" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="T5" s="109"/>
-      <c r="U5" s="109"/>
-      <c r="V5" s="109"/>
-      <c r="W5" s="109"/>
-      <c r="X5" s="109"/>
-      <c r="Y5" s="109"/>
-      <c r="Z5" s="109"/>
-      <c r="AA5" s="109"/>
-      <c r="AB5" s="109"/>
-      <c r="AC5" s="109"/>
-      <c r="AD5" s="109"/>
-      <c r="AE5" s="109"/>
-      <c r="AF5" s="109"/>
-      <c r="AG5" s="109"/>
-      <c r="AH5" s="110"/>
-      <c r="AI5" s="96" t="s">
+      <c r="T5" s="105"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="105"/>
+      <c r="W5" s="105"/>
+      <c r="X5" s="105"/>
+      <c r="Y5" s="105"/>
+      <c r="Z5" s="105"/>
+      <c r="AA5" s="105"/>
+      <c r="AB5" s="105"/>
+      <c r="AC5" s="105"/>
+      <c r="AD5" s="105"/>
+      <c r="AE5" s="105"/>
+      <c r="AF5" s="105"/>
+      <c r="AG5" s="105"/>
+      <c r="AH5" s="106"/>
+      <c r="AI5" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="AJ5" s="97"/>
-      <c r="AK5" s="97"/>
-      <c r="AL5" s="97"/>
-      <c r="AM5" s="97"/>
-      <c r="AN5" s="97"/>
-      <c r="AO5" s="97"/>
-      <c r="AP5" s="97"/>
-      <c r="AQ5" s="97"/>
-      <c r="AR5" s="97"/>
-      <c r="AS5" s="97"/>
-      <c r="AT5" s="97"/>
-      <c r="AU5" s="97"/>
-      <c r="AV5" s="97"/>
-      <c r="AW5" s="98"/>
-      <c r="AX5" s="96" t="s">
+      <c r="AJ5" s="93"/>
+      <c r="AK5" s="93"/>
+      <c r="AL5" s="93"/>
+      <c r="AM5" s="93"/>
+      <c r="AN5" s="93"/>
+      <c r="AO5" s="93"/>
+      <c r="AP5" s="93"/>
+      <c r="AQ5" s="93"/>
+      <c r="AR5" s="93"/>
+      <c r="AS5" s="93"/>
+      <c r="AT5" s="93"/>
+      <c r="AU5" s="93"/>
+      <c r="AV5" s="93"/>
+      <c r="AW5" s="94"/>
+      <c r="AX5" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="AY5" s="97"/>
-      <c r="AZ5" s="97"/>
-      <c r="BA5" s="97"/>
-      <c r="BB5" s="97"/>
-      <c r="BC5" s="97"/>
-      <c r="BD5" s="97"/>
-      <c r="BE5" s="97"/>
-      <c r="BF5" s="97"/>
-      <c r="BG5" s="97"/>
-      <c r="BH5" s="97"/>
-      <c r="BI5" s="97"/>
-      <c r="BJ5" s="98"/>
-      <c r="BK5" s="82" t="s">
+      <c r="AY5" s="93"/>
+      <c r="AZ5" s="93"/>
+      <c r="BA5" s="93"/>
+      <c r="BB5" s="93"/>
+      <c r="BC5" s="93"/>
+      <c r="BD5" s="93"/>
+      <c r="BE5" s="93"/>
+      <c r="BF5" s="93"/>
+      <c r="BG5" s="93"/>
+      <c r="BH5" s="93"/>
+      <c r="BI5" s="93"/>
+      <c r="BJ5" s="94"/>
+      <c r="BK5" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="BL5" s="83"/>
-      <c r="BM5" s="84"/>
-      <c r="BN5" s="82" t="s">
+      <c r="BL5" s="77"/>
+      <c r="BM5" s="78"/>
+      <c r="BN5" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="BO5" s="83"/>
-      <c r="BP5" s="83"/>
-      <c r="BQ5" s="84"/>
-      <c r="BR5" s="82" t="s">
+      <c r="BO5" s="77"/>
+      <c r="BP5" s="77"/>
+      <c r="BQ5" s="78"/>
+      <c r="BR5" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="BS5" s="83"/>
-      <c r="BT5" s="83"/>
-      <c r="BU5" s="84"/>
+      <c r="BS5" s="77"/>
+      <c r="BT5" s="77"/>
+      <c r="BU5" s="78"/>
     </row>
     <row r="6" spans="1:74" s="4" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A6" s="75"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-      <c r="O6" s="112"/>
-      <c r="P6" s="112"/>
-      <c r="Q6" s="112"/>
-      <c r="R6" s="113"/>
-      <c r="S6" s="111"/>
-      <c r="T6" s="112"/>
-      <c r="U6" s="112"/>
-      <c r="V6" s="112"/>
-      <c r="W6" s="112"/>
-      <c r="X6" s="112"/>
-      <c r="Y6" s="112"/>
-      <c r="Z6" s="112"/>
-      <c r="AA6" s="112"/>
-      <c r="AB6" s="112"/>
-      <c r="AC6" s="112"/>
-      <c r="AD6" s="112"/>
-      <c r="AE6" s="112"/>
-      <c r="AF6" s="112"/>
-      <c r="AG6" s="112"/>
-      <c r="AH6" s="113"/>
-      <c r="AI6" s="99"/>
-      <c r="AJ6" s="100"/>
-      <c r="AK6" s="100"/>
-      <c r="AL6" s="100"/>
-      <c r="AM6" s="100"/>
-      <c r="AN6" s="100"/>
-      <c r="AO6" s="100"/>
-      <c r="AP6" s="100"/>
-      <c r="AQ6" s="100"/>
-      <c r="AR6" s="100"/>
-      <c r="AS6" s="100"/>
-      <c r="AT6" s="100"/>
-      <c r="AU6" s="100"/>
-      <c r="AV6" s="100"/>
-      <c r="AW6" s="101"/>
-      <c r="AX6" s="99"/>
-      <c r="AY6" s="100"/>
-      <c r="AZ6" s="100"/>
-      <c r="BA6" s="100"/>
-      <c r="BB6" s="100"/>
-      <c r="BC6" s="100"/>
-      <c r="BD6" s="100"/>
-      <c r="BE6" s="100"/>
-      <c r="BF6" s="100"/>
-      <c r="BG6" s="100"/>
-      <c r="BH6" s="100"/>
-      <c r="BI6" s="100"/>
-      <c r="BJ6" s="101"/>
-      <c r="BK6" s="85"/>
-      <c r="BL6" s="86"/>
-      <c r="BM6" s="87"/>
-      <c r="BN6" s="85"/>
-      <c r="BO6" s="86"/>
-      <c r="BP6" s="86"/>
-      <c r="BQ6" s="87"/>
-      <c r="BR6" s="85"/>
-      <c r="BS6" s="86"/>
-      <c r="BT6" s="86"/>
-      <c r="BU6" s="87"/>
+      <c r="A6" s="107"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="109"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="108"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="107"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="108"/>
+      <c r="V6" s="108"/>
+      <c r="W6" s="108"/>
+      <c r="X6" s="108"/>
+      <c r="Y6" s="108"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="108"/>
+      <c r="AB6" s="108"/>
+      <c r="AC6" s="108"/>
+      <c r="AD6" s="108"/>
+      <c r="AE6" s="108"/>
+      <c r="AF6" s="108"/>
+      <c r="AG6" s="108"/>
+      <c r="AH6" s="109"/>
+      <c r="AI6" s="95"/>
+      <c r="AJ6" s="96"/>
+      <c r="AK6" s="96"/>
+      <c r="AL6" s="96"/>
+      <c r="AM6" s="96"/>
+      <c r="AN6" s="96"/>
+      <c r="AO6" s="96"/>
+      <c r="AP6" s="96"/>
+      <c r="AQ6" s="96"/>
+      <c r="AR6" s="96"/>
+      <c r="AS6" s="96"/>
+      <c r="AT6" s="96"/>
+      <c r="AU6" s="96"/>
+      <c r="AV6" s="96"/>
+      <c r="AW6" s="97"/>
+      <c r="AX6" s="95"/>
+      <c r="AY6" s="96"/>
+      <c r="AZ6" s="96"/>
+      <c r="BA6" s="96"/>
+      <c r="BB6" s="96"/>
+      <c r="BC6" s="96"/>
+      <c r="BD6" s="96"/>
+      <c r="BE6" s="96"/>
+      <c r="BF6" s="96"/>
+      <c r="BG6" s="96"/>
+      <c r="BH6" s="96"/>
+      <c r="BI6" s="96"/>
+      <c r="BJ6" s="97"/>
+      <c r="BK6" s="79"/>
+      <c r="BL6" s="80"/>
+      <c r="BM6" s="81"/>
+      <c r="BN6" s="79"/>
+      <c r="BO6" s="80"/>
+      <c r="BP6" s="80"/>
+      <c r="BQ6" s="81"/>
+      <c r="BR6" s="79"/>
+      <c r="BS6" s="80"/>
+      <c r="BT6" s="80"/>
+      <c r="BU6" s="81"/>
     </row>
     <row r="7" spans="1:74" ht="14.4" customHeight="1">
       <c r="A7" s="25">
@@ -2612,61 +2551,61 @@
       <c r="E7" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="30"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="69"/>
       <c r="L7" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="31" t="s">
         <v>29</v>
       </c>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="31" t="s">
+        <v>27</v>
+      </c>
       <c r="T7" s="32"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="25" t="s">
-        <v>54</v>
+      <c r="U7" s="32"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="32"/>
+      <c r="X7" s="32"/>
+      <c r="Y7" s="32"/>
+      <c r="Z7" s="32"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="32"/>
+      <c r="AF7" s="32"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="69"/>
+      <c r="AI7" s="31" t="s">
+        <v>48</v>
       </c>
-      <c r="AJ7" s="26"/>
-      <c r="AK7" s="35"/>
-      <c r="AL7" s="35"/>
-      <c r="AM7" s="35"/>
-      <c r="AN7" s="35"/>
-      <c r="AO7" s="35"/>
-      <c r="AP7" s="35"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
-      <c r="AV7" s="29"/>
-      <c r="AW7" s="30"/>
-      <c r="AX7" s="66" t="s">
-        <v>46</v>
+      <c r="AJ7" s="32"/>
+      <c r="AK7" s="32"/>
+      <c r="AL7" s="32"/>
+      <c r="AM7" s="32"/>
+      <c r="AN7" s="32"/>
+      <c r="AO7" s="32"/>
+      <c r="AP7" s="32"/>
+      <c r="AQ7" s="32"/>
+      <c r="AR7" s="32"/>
+      <c r="AS7" s="32"/>
+      <c r="AT7" s="32"/>
+      <c r="AU7" s="32"/>
+      <c r="AV7" s="32"/>
+      <c r="AW7" s="69"/>
+      <c r="AX7" s="36" t="s">
+        <v>40</v>
       </c>
-      <c r="AY7" s="67"/>
-      <c r="AZ7" s="67"/>
+      <c r="AY7" s="35"/>
+      <c r="AZ7" s="32"/>
       <c r="BA7" s="32"/>
       <c r="BB7" s="32"/>
       <c r="BC7" s="32"/>
@@ -2695,70 +2634,70 @@
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="7" t="s">
-        <v>26</v>
+      <c r="E8" s="10" t="s">
+        <v>18</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
       <c r="S8" s="10" t="s">
         <v>19</v>
       </c>
       <c r="T8" s="44"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="43"/>
-      <c r="Z8" s="43"/>
-      <c r="AA8" s="43"/>
-      <c r="AB8" s="43"/>
-      <c r="AC8" s="43"/>
-      <c r="AD8" s="43"/>
-      <c r="AE8" s="43"/>
-      <c r="AF8" s="43"/>
-      <c r="AG8" s="43"/>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="60" t="s">
-        <v>55</v>
+      <c r="U8" s="44"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="44"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="44"/>
+      <c r="AB8" s="44"/>
+      <c r="AC8" s="44"/>
+      <c r="AD8" s="44"/>
+      <c r="AE8" s="44"/>
+      <c r="AF8" s="44"/>
+      <c r="AG8" s="44"/>
+      <c r="AH8" s="40"/>
+      <c r="AI8" s="10" t="s">
+        <v>49</v>
       </c>
-      <c r="AJ8" s="59"/>
-      <c r="AK8" s="46"/>
-      <c r="AL8" s="46"/>
-      <c r="AM8" s="46"/>
-      <c r="AN8" s="46"/>
-      <c r="AO8" s="46"/>
-      <c r="AP8" s="46"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
-      <c r="AT8" s="43"/>
-      <c r="AU8" s="43"/>
-      <c r="AV8" s="43"/>
-      <c r="AW8" s="9"/>
-      <c r="AX8" s="58"/>
-      <c r="AY8" s="59"/>
-      <c r="AZ8" s="59"/>
-      <c r="BA8" s="46"/>
-      <c r="BB8" s="46"/>
-      <c r="BC8" s="46"/>
-      <c r="BD8" s="46"/>
-      <c r="BE8" s="46"/>
-      <c r="BF8" s="43"/>
-      <c r="BG8" s="43"/>
-      <c r="BH8" s="46"/>
-      <c r="BI8" s="46"/>
-      <c r="BJ8" s="46"/>
+      <c r="AJ8" s="44"/>
+      <c r="AK8" s="44"/>
+      <c r="AL8" s="44"/>
+      <c r="AM8" s="44"/>
+      <c r="AN8" s="44"/>
+      <c r="AO8" s="44"/>
+      <c r="AP8" s="44"/>
+      <c r="AQ8" s="44"/>
+      <c r="AR8" s="44"/>
+      <c r="AS8" s="44"/>
+      <c r="AT8" s="44"/>
+      <c r="AU8" s="44"/>
+      <c r="AV8" s="44"/>
+      <c r="AW8" s="40"/>
+      <c r="AX8" s="14"/>
+      <c r="AY8" s="46"/>
+      <c r="AZ8" s="44"/>
+      <c r="BA8" s="44"/>
+      <c r="BB8" s="44"/>
+      <c r="BC8" s="44"/>
+      <c r="BD8" s="44"/>
+      <c r="BE8" s="44"/>
+      <c r="BF8" s="44"/>
+      <c r="BG8" s="44"/>
+      <c r="BH8" s="44"/>
+      <c r="BI8" s="44"/>
+      <c r="BJ8" s="44"/>
       <c r="BK8" s="16"/>
       <c r="BL8" s="47"/>
       <c r="BM8" s="17"/>
@@ -2777,37 +2716,39 @@
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
       <c r="S9" s="10"/>
       <c r="T9" s="44"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="43"/>
-      <c r="AA9" s="43"/>
-      <c r="AB9" s="43"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="43"/>
-      <c r="AF9" s="43"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="13"/>
-      <c r="AI9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="44"/>
+      <c r="AA9" s="44"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44"/>
+      <c r="AE9" s="44"/>
+      <c r="AF9" s="44"/>
+      <c r="AG9" s="44"/>
+      <c r="AH9" s="40"/>
+      <c r="AI9" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="AJ9" s="44"/>
       <c r="AK9" s="44"/>
       <c r="AL9" s="44"/>
@@ -2821,20 +2762,20 @@
       <c r="AT9" s="44"/>
       <c r="AU9" s="44"/>
       <c r="AV9" s="44"/>
-      <c r="AW9" s="44"/>
-      <c r="AX9" s="49"/>
-      <c r="AY9" s="48"/>
+      <c r="AW9" s="40"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="46"/>
       <c r="AZ9" s="44"/>
       <c r="BA9" s="44"/>
-      <c r="BB9" s="46"/>
-      <c r="BC9" s="46"/>
-      <c r="BD9" s="46"/>
-      <c r="BE9" s="46"/>
-      <c r="BF9" s="43"/>
-      <c r="BG9" s="43"/>
-      <c r="BH9" s="46"/>
-      <c r="BI9" s="46"/>
-      <c r="BJ9" s="46"/>
+      <c r="BB9" s="44"/>
+      <c r="BC9" s="44"/>
+      <c r="BD9" s="44"/>
+      <c r="BE9" s="44"/>
+      <c r="BF9" s="44"/>
+      <c r="BG9" s="44"/>
+      <c r="BH9" s="44"/>
+      <c r="BI9" s="44"/>
+      <c r="BJ9" s="44"/>
       <c r="BK9" s="16"/>
       <c r="BL9" s="47"/>
       <c r="BM9" s="17"/>
@@ -2849,43 +2790,43 @@
       <c r="BV9" s="11"/>
     </row>
     <row r="10" spans="1:74" ht="14.4" customHeight="1">
-      <c r="A10" s="81" t="s">
-        <v>81</v>
+      <c r="A10" s="75" t="s">
+        <v>66</v>
       </c>
       <c r="B10" s="53"/>
-      <c r="C10" s="73"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="54"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
       <c r="S10" s="55"/>
       <c r="T10" s="56"/>
-      <c r="U10" s="21"/>
-      <c r="V10" s="21"/>
-      <c r="W10" s="21"/>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="19"/>
-      <c r="AG10" s="19"/>
-      <c r="AH10" s="22"/>
-      <c r="AI10" s="56"/>
+      <c r="U10" s="56"/>
+      <c r="V10" s="56"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="56"/>
+      <c r="Z10" s="56"/>
+      <c r="AA10" s="56"/>
+      <c r="AB10" s="56"/>
+      <c r="AC10" s="56"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="56"/>
+      <c r="AH10" s="57"/>
+      <c r="AI10" s="55"/>
       <c r="AJ10" s="56"/>
       <c r="AK10" s="56"/>
       <c r="AL10" s="56"/>
@@ -2899,23 +2840,23 @@
       <c r="AT10" s="56"/>
       <c r="AU10" s="56"/>
       <c r="AV10" s="56"/>
-      <c r="AW10" s="56"/>
-      <c r="AX10" s="50"/>
-      <c r="AY10" s="51"/>
+      <c r="AW10" s="57"/>
+      <c r="AX10" s="23"/>
+      <c r="AY10" s="24"/>
       <c r="AZ10" s="56"/>
       <c r="BA10" s="56"/>
-      <c r="BB10" s="24"/>
-      <c r="BC10" s="24"/>
-      <c r="BD10" s="24"/>
-      <c r="BE10" s="24"/>
-      <c r="BF10" s="19"/>
-      <c r="BG10" s="19"/>
-      <c r="BH10" s="24"/>
-      <c r="BI10" s="24"/>
-      <c r="BJ10" s="24"/>
-      <c r="BK10" s="69"/>
-      <c r="BL10" s="70"/>
-      <c r="BM10" s="71"/>
+      <c r="BB10" s="56"/>
+      <c r="BC10" s="56"/>
+      <c r="BD10" s="56"/>
+      <c r="BE10" s="56"/>
+      <c r="BF10" s="56"/>
+      <c r="BG10" s="56"/>
+      <c r="BH10" s="56"/>
+      <c r="BI10" s="56"/>
+      <c r="BJ10" s="56"/>
+      <c r="BK10" s="66"/>
+      <c r="BL10" s="67"/>
+      <c r="BM10" s="68"/>
       <c r="BN10" s="23"/>
       <c r="BO10" s="24"/>
       <c r="BP10" s="24"/>
@@ -2936,61 +2877,61 @@
       <c r="E11" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="72"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="30"/>
       <c r="L11" s="28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
       <c r="S11" s="31" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T11" s="32"/>
-      <c r="U11" s="32"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="32"/>
-      <c r="X11" s="32"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="32"/>
-      <c r="AA11" s="32"/>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="32"/>
-      <c r="AD11" s="32"/>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="32"/>
-      <c r="AG11" s="32"/>
-      <c r="AH11" s="72"/>
-      <c r="AI11" s="31" t="s">
-        <v>56</v>
+      <c r="U11" s="33"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="33"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="29"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="29"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="25" t="s">
+        <v>46</v>
       </c>
-      <c r="AJ11" s="32"/>
-      <c r="AK11" s="32"/>
-      <c r="AL11" s="32"/>
-      <c r="AM11" s="32"/>
-      <c r="AN11" s="32"/>
-      <c r="AO11" s="32"/>
-      <c r="AP11" s="32"/>
-      <c r="AQ11" s="32"/>
-      <c r="AR11" s="32"/>
-      <c r="AS11" s="32"/>
-      <c r="AT11" s="32"/>
-      <c r="AU11" s="32"/>
-      <c r="AV11" s="32"/>
-      <c r="AW11" s="72"/>
-      <c r="AX11" s="36" t="s">
-        <v>47</v>
+      <c r="AJ11" s="26"/>
+      <c r="AK11" s="35"/>
+      <c r="AL11" s="35"/>
+      <c r="AM11" s="35"/>
+      <c r="AN11" s="35"/>
+      <c r="AO11" s="35"/>
+      <c r="AP11" s="35"/>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="29"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="29"/>
+      <c r="AV11" s="29"/>
+      <c r="AW11" s="30"/>
+      <c r="AX11" s="63" t="s">
+        <v>39</v>
       </c>
-      <c r="AY11" s="35"/>
-      <c r="AZ11" s="32"/>
+      <c r="AY11" s="64"/>
+      <c r="AZ11" s="64"/>
       <c r="BA11" s="32"/>
       <c r="BB11" s="32"/>
       <c r="BC11" s="32"/>
@@ -3003,85 +2944,85 @@
       <c r="BJ11" s="32"/>
       <c r="BK11" s="31"/>
       <c r="BL11" s="32"/>
-      <c r="BM11" s="72"/>
+      <c r="BM11" s="69"/>
       <c r="BN11" s="31"/>
       <c r="BO11" s="32"/>
       <c r="BP11" s="32"/>
-      <c r="BQ11" s="72"/>
+      <c r="BQ11" s="69"/>
       <c r="BR11" s="31"/>
       <c r="BS11" s="32"/>
       <c r="BT11" s="32"/>
-      <c r="BU11" s="72"/>
+      <c r="BU11" s="69"/>
     </row>
     <row r="12" spans="1:74" s="11" customFormat="1" ht="14.4" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="6"/>
-      <c r="E12" s="10" t="s">
-        <v>18</v>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
       </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
       <c r="S12" s="10" t="s">
         <v>19</v>
       </c>
       <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="44"/>
-      <c r="W12" s="44"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="44"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="44"/>
-      <c r="AE12" s="44"/>
-      <c r="AF12" s="44"/>
-      <c r="AG12" s="44"/>
-      <c r="AH12" s="40"/>
-      <c r="AI12" s="10" t="s">
-        <v>57</v>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="13"/>
+      <c r="AI12" s="60" t="s">
+        <v>47</v>
       </c>
-      <c r="AJ12" s="44"/>
-      <c r="AK12" s="44"/>
-      <c r="AL12" s="44"/>
-      <c r="AM12" s="44"/>
-      <c r="AN12" s="44"/>
-      <c r="AO12" s="44"/>
-      <c r="AP12" s="44"/>
-      <c r="AQ12" s="44"/>
-      <c r="AR12" s="44"/>
-      <c r="AS12" s="44"/>
-      <c r="AT12" s="44"/>
-      <c r="AU12" s="44"/>
-      <c r="AV12" s="44"/>
-      <c r="AW12" s="40"/>
-      <c r="AX12" s="14"/>
-      <c r="AY12" s="46"/>
-      <c r="AZ12" s="44"/>
-      <c r="BA12" s="44"/>
-      <c r="BB12" s="44"/>
-      <c r="BC12" s="44"/>
-      <c r="BD12" s="44"/>
-      <c r="BE12" s="44"/>
-      <c r="BF12" s="44"/>
-      <c r="BG12" s="44"/>
-      <c r="BH12" s="44"/>
-      <c r="BI12" s="44"/>
-      <c r="BJ12" s="44"/>
+      <c r="AJ12" s="59"/>
+      <c r="AK12" s="46"/>
+      <c r="AL12" s="46"/>
+      <c r="AM12" s="46"/>
+      <c r="AN12" s="46"/>
+      <c r="AO12" s="46"/>
+      <c r="AP12" s="46"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="9"/>
+      <c r="AX12" s="58"/>
+      <c r="AY12" s="59"/>
+      <c r="AZ12" s="59"/>
+      <c r="BA12" s="46"/>
+      <c r="BB12" s="46"/>
+      <c r="BC12" s="46"/>
+      <c r="BD12" s="46"/>
+      <c r="BE12" s="46"/>
+      <c r="BF12" s="43"/>
+      <c r="BG12" s="43"/>
+      <c r="BH12" s="46"/>
+      <c r="BI12" s="46"/>
+      <c r="BJ12" s="46"/>
       <c r="BK12" s="10"/>
       <c r="BL12" s="44"/>
       <c r="BM12" s="40"/>
@@ -3099,39 +3040,37 @@
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
       <c r="S13" s="10"/>
       <c r="T13" s="44"/>
-      <c r="U13" s="44"/>
-      <c r="V13" s="44"/>
-      <c r="W13" s="44"/>
-      <c r="X13" s="44"/>
-      <c r="Y13" s="44"/>
-      <c r="Z13" s="44"/>
-      <c r="AA13" s="44"/>
-      <c r="AB13" s="44"/>
-      <c r="AC13" s="44"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="44"/>
-      <c r="AF13" s="44"/>
-      <c r="AG13" s="44"/>
-      <c r="AH13" s="40"/>
-      <c r="AI13" s="10" t="s">
-        <v>58</v>
-      </c>
+      <c r="U13" s="45"/>
+      <c r="V13" s="45"/>
+      <c r="W13" s="45"/>
+      <c r="X13" s="45"/>
+      <c r="Y13" s="43"/>
+      <c r="Z13" s="43"/>
+      <c r="AA13" s="43"/>
+      <c r="AB13" s="43"/>
+      <c r="AC13" s="43"/>
+      <c r="AD13" s="43"/>
+      <c r="AE13" s="43"/>
+      <c r="AF13" s="43"/>
+      <c r="AG13" s="43"/>
+      <c r="AH13" s="13"/>
+      <c r="AI13" s="44"/>
       <c r="AJ13" s="44"/>
       <c r="AK13" s="44"/>
       <c r="AL13" s="44"/>
@@ -3145,20 +3084,20 @@
       <c r="AT13" s="44"/>
       <c r="AU13" s="44"/>
       <c r="AV13" s="44"/>
-      <c r="AW13" s="40"/>
-      <c r="AX13" s="14"/>
-      <c r="AY13" s="46"/>
+      <c r="AW13" s="44"/>
+      <c r="AX13" s="49"/>
+      <c r="AY13" s="48"/>
       <c r="AZ13" s="44"/>
       <c r="BA13" s="44"/>
-      <c r="BB13" s="44"/>
-      <c r="BC13" s="44"/>
-      <c r="BD13" s="44"/>
-      <c r="BE13" s="44"/>
-      <c r="BF13" s="44"/>
-      <c r="BG13" s="44"/>
-      <c r="BH13" s="44"/>
-      <c r="BI13" s="44"/>
-      <c r="BJ13" s="44"/>
+      <c r="BB13" s="46"/>
+      <c r="BC13" s="46"/>
+      <c r="BD13" s="46"/>
+      <c r="BE13" s="46"/>
+      <c r="BF13" s="43"/>
+      <c r="BG13" s="43"/>
+      <c r="BH13" s="46"/>
+      <c r="BI13" s="46"/>
+      <c r="BJ13" s="46"/>
       <c r="BK13" s="10"/>
       <c r="BL13" s="44"/>
       <c r="BM13" s="40"/>
@@ -3172,43 +3111,43 @@
       <c r="BU13" s="40"/>
     </row>
     <row r="14" spans="1:74" s="11" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A14" s="81" t="s">
-        <v>81</v>
+      <c r="A14" s="75" t="s">
+        <v>66</v>
       </c>
       <c r="B14" s="53"/>
-      <c r="C14" s="44"/>
+      <c r="C14" s="70"/>
       <c r="D14" s="54"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="56"/>
-      <c r="N14" s="56"/>
-      <c r="O14" s="56"/>
-      <c r="P14" s="56"/>
-      <c r="Q14" s="56"/>
-      <c r="R14" s="56"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
       <c r="S14" s="55"/>
       <c r="T14" s="56"/>
-      <c r="U14" s="56"/>
-      <c r="V14" s="56"/>
-      <c r="W14" s="56"/>
-      <c r="X14" s="56"/>
-      <c r="Y14" s="56"/>
-      <c r="Z14" s="56"/>
-      <c r="AA14" s="56"/>
-      <c r="AB14" s="56"/>
-      <c r="AC14" s="56"/>
-      <c r="AD14" s="56"/>
-      <c r="AE14" s="56"/>
-      <c r="AF14" s="56"/>
-      <c r="AG14" s="56"/>
-      <c r="AH14" s="57"/>
-      <c r="AI14" s="55"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="19"/>
+      <c r="AA14" s="19"/>
+      <c r="AB14" s="19"/>
+      <c r="AC14" s="19"/>
+      <c r="AD14" s="19"/>
+      <c r="AE14" s="19"/>
+      <c r="AF14" s="19"/>
+      <c r="AG14" s="19"/>
+      <c r="AH14" s="22"/>
+      <c r="AI14" s="56"/>
       <c r="AJ14" s="56"/>
       <c r="AK14" s="56"/>
       <c r="AL14" s="56"/>
@@ -3222,20 +3161,20 @@
       <c r="AT14" s="56"/>
       <c r="AU14" s="56"/>
       <c r="AV14" s="56"/>
-      <c r="AW14" s="57"/>
-      <c r="AX14" s="23"/>
-      <c r="AY14" s="24"/>
+      <c r="AW14" s="56"/>
+      <c r="AX14" s="50"/>
+      <c r="AY14" s="51"/>
       <c r="AZ14" s="56"/>
       <c r="BA14" s="56"/>
-      <c r="BB14" s="56"/>
-      <c r="BC14" s="56"/>
-      <c r="BD14" s="56"/>
-      <c r="BE14" s="56"/>
-      <c r="BF14" s="56"/>
-      <c r="BG14" s="56"/>
-      <c r="BH14" s="56"/>
-      <c r="BI14" s="56"/>
-      <c r="BJ14" s="56"/>
+      <c r="BB14" s="24"/>
+      <c r="BC14" s="24"/>
+      <c r="BD14" s="24"/>
+      <c r="BE14" s="24"/>
+      <c r="BF14" s="19"/>
+      <c r="BG14" s="19"/>
+      <c r="BH14" s="24"/>
+      <c r="BI14" s="24"/>
+      <c r="BJ14" s="24"/>
       <c r="BK14" s="55"/>
       <c r="BL14" s="56"/>
       <c r="BM14" s="57"/>
@@ -3263,9 +3202,9 @@
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
-      <c r="K15" s="72"/>
+      <c r="K15" s="69"/>
       <c r="L15" s="28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M15" s="32"/>
       <c r="N15" s="32"/>
@@ -3274,10 +3213,10 @@
       <c r="Q15" s="32"/>
       <c r="R15" s="44"/>
       <c r="S15" s="31" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
-      <c r="T15" s="74"/>
-      <c r="U15" s="74"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
       <c r="V15" s="32"/>
       <c r="W15" s="32"/>
       <c r="X15" s="32"/>
@@ -3290,9 +3229,9 @@
       <c r="AE15" s="32"/>
       <c r="AF15" s="32"/>
       <c r="AG15" s="32"/>
-      <c r="AH15" s="72"/>
+      <c r="AH15" s="69"/>
       <c r="AI15" s="25" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AJ15" s="32"/>
       <c r="AK15" s="32"/>
@@ -3307,7 +3246,7 @@
       <c r="AT15" s="32"/>
       <c r="AU15" s="32"/>
       <c r="AV15" s="32"/>
-      <c r="AW15" s="72"/>
+      <c r="AW15" s="69"/>
       <c r="AX15" s="36"/>
       <c r="AY15" s="35"/>
       <c r="AZ15" s="32"/>
@@ -3323,15 +3262,15 @@
       <c r="BJ15" s="32"/>
       <c r="BK15" s="31"/>
       <c r="BL15" s="32"/>
-      <c r="BM15" s="72"/>
+      <c r="BM15" s="69"/>
       <c r="BN15" s="31"/>
       <c r="BO15" s="32"/>
       <c r="BP15" s="32"/>
-      <c r="BQ15" s="72"/>
+      <c r="BQ15" s="69"/>
       <c r="BR15" s="31"/>
       <c r="BS15" s="32"/>
       <c r="BT15" s="32"/>
-      <c r="BU15" s="72"/>
+      <c r="BU15" s="69"/>
       <c r="BV15" s="11"/>
     </row>
     <row r="16" spans="1:74" ht="14.4" customHeight="1">
@@ -3358,8 +3297,8 @@
       <c r="S16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="T16" s="73"/>
-      <c r="U16" s="73"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="70"/>
       <c r="V16" s="44"/>
       <c r="W16" s="44"/>
       <c r="X16" s="44"/>
@@ -3374,7 +3313,7 @@
       <c r="AG16" s="44"/>
       <c r="AH16" s="40"/>
       <c r="AI16" s="60" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="AJ16" s="44"/>
       <c r="AK16" s="44"/>
@@ -3422,7 +3361,7 @@
       <c r="C17" s="42"/>
       <c r="D17" s="6"/>
       <c r="E17" s="10" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="44"/>
@@ -3438,8 +3377,8 @@
       <c r="Q17" s="44"/>
       <c r="R17" s="44"/>
       <c r="S17" s="10"/>
-      <c r="T17" s="73"/>
-      <c r="U17" s="73"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
       <c r="V17" s="44"/>
       <c r="W17" s="44"/>
       <c r="X17" s="44"/>
@@ -3499,9 +3438,6 @@
       <c r="B18" s="42"/>
       <c r="C18" s="42"/>
       <c r="D18" s="6"/>
-      <c r="E18" s="10" t="s">
-        <v>28</v>
-      </c>
       <c r="F18" s="44"/>
       <c r="G18" s="44"/>
       <c r="H18" s="44"/>
@@ -3516,8 +3452,8 @@
       <c r="Q18" s="44"/>
       <c r="R18" s="44"/>
       <c r="S18" s="10"/>
-      <c r="T18" s="73"/>
-      <c r="U18" s="73"/>
+      <c r="T18" s="70"/>
+      <c r="U18" s="70"/>
       <c r="V18" s="44"/>
       <c r="W18" s="44"/>
       <c r="X18" s="44"/>
@@ -3548,9 +3484,7 @@
       <c r="AU18" s="44"/>
       <c r="AV18" s="44"/>
       <c r="AW18" s="40"/>
-      <c r="AX18" s="14" t="s">
-        <v>45</v>
-      </c>
+      <c r="AX18" s="14"/>
       <c r="AY18" s="46"/>
       <c r="AZ18" s="44"/>
       <c r="BA18" s="44"/>
@@ -3626,9 +3560,7 @@
       <c r="AU19" s="44"/>
       <c r="AV19" s="44"/>
       <c r="AW19" s="40"/>
-      <c r="AX19" s="14" t="s">
-        <v>44</v>
-      </c>
+      <c r="AX19" s="14"/>
       <c r="AY19" s="46"/>
       <c r="AZ19" s="44"/>
       <c r="BA19" s="44"/>
@@ -3704,9 +3636,7 @@
       <c r="AU20" s="44"/>
       <c r="AV20" s="44"/>
       <c r="AW20" s="40"/>
-      <c r="AX20" s="14" t="s">
-        <v>24</v>
-      </c>
+      <c r="AX20" s="14"/>
       <c r="AY20" s="46"/>
       <c r="AZ20" s="44"/>
       <c r="BA20" s="44"/>
@@ -3844,7 +3774,7 @@
       <c r="AG22" s="44"/>
       <c r="AH22" s="40"/>
       <c r="AI22" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ22" s="44"/>
       <c r="AK22" s="44"/>
@@ -3860,9 +3790,7 @@
       <c r="AU22" s="44"/>
       <c r="AV22" s="44"/>
       <c r="AW22" s="40"/>
-      <c r="AX22" s="14" t="s">
-        <v>48</v>
-      </c>
+      <c r="AX22" s="14"/>
       <c r="AY22" s="46"/>
       <c r="AZ22" s="44"/>
       <c r="BA22" s="44"/>
@@ -4000,7 +3928,7 @@
       <c r="AG24" s="44"/>
       <c r="AH24" s="40"/>
       <c r="AI24" s="10" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AJ24" s="44"/>
       <c r="AK24" s="44"/>
@@ -4017,7 +3945,7 @@
       <c r="AV24" s="44"/>
       <c r="AW24" s="40"/>
       <c r="AX24" s="14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="AY24" s="46"/>
       <c r="AZ24" s="44"/>
@@ -4080,7 +4008,7 @@
       <c r="AG25" s="44"/>
       <c r="AH25" s="40"/>
       <c r="AI25" s="10" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AJ25" s="44"/>
       <c r="AK25" s="44"/>
@@ -4123,11 +4051,11 @@
       <c r="BV25" s="11"/>
     </row>
     <row r="26" spans="1:74" ht="14.4" customHeight="1">
-      <c r="A26" s="81" t="s">
-        <v>81</v>
+      <c r="A26" s="75" t="s">
+        <v>66</v>
       </c>
       <c r="B26" s="53"/>
-      <c r="C26" s="68"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="54"/>
       <c r="E26" s="10"/>
       <c r="F26" s="44"/>
@@ -4208,16 +4136,16 @@
       <c r="C27" s="26"/>
       <c r="D27" s="27"/>
       <c r="E27" s="28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
       <c r="H27" s="32"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
-      <c r="K27" s="72"/>
+      <c r="K27" s="69"/>
       <c r="L27" s="28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M27" s="32"/>
       <c r="N27" s="32"/>
@@ -4226,10 +4154,10 @@
       <c r="Q27" s="32"/>
       <c r="R27" s="32"/>
       <c r="S27" s="31" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
-      <c r="T27" s="74"/>
-      <c r="U27" s="74"/>
+      <c r="T27" s="71"/>
+      <c r="U27" s="71"/>
       <c r="V27" s="32"/>
       <c r="W27" s="32"/>
       <c r="X27" s="32"/>
@@ -4242,9 +4170,9 @@
       <c r="AE27" s="32"/>
       <c r="AF27" s="32"/>
       <c r="AG27" s="32"/>
-      <c r="AH27" s="72"/>
+      <c r="AH27" s="69"/>
       <c r="AI27" s="31" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AJ27" s="32"/>
       <c r="AK27" s="32"/>
@@ -4259,9 +4187,9 @@
       <c r="AT27" s="32"/>
       <c r="AU27" s="32"/>
       <c r="AV27" s="32"/>
-      <c r="AW27" s="72"/>
+      <c r="AW27" s="69"/>
       <c r="AX27" s="36" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AY27" s="35"/>
       <c r="AZ27" s="32"/>
@@ -4274,18 +4202,18 @@
       <c r="BG27" s="32"/>
       <c r="BH27" s="32"/>
       <c r="BI27" s="32"/>
-      <c r="BJ27" s="32"/>
+      <c r="BJ27" s="69"/>
       <c r="BK27" s="31"/>
       <c r="BL27" s="32"/>
-      <c r="BM27" s="72"/>
+      <c r="BM27" s="69"/>
       <c r="BN27" s="31"/>
       <c r="BO27" s="32"/>
       <c r="BP27" s="32"/>
-      <c r="BQ27" s="72"/>
+      <c r="BQ27" s="69"/>
       <c r="BR27" s="31"/>
       <c r="BS27" s="32"/>
       <c r="BT27" s="32"/>
-      <c r="BU27" s="72"/>
+      <c r="BU27" s="69"/>
       <c r="BV27" s="11"/>
     </row>
     <row r="28" spans="1:74" ht="14.4" customHeight="1">
@@ -4293,10 +4221,10 @@
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
       <c r="D28" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F28" s="44"/>
       <c r="G28" s="44"/>
@@ -4312,8 +4240,8 @@
       <c r="Q28" s="44"/>
       <c r="R28" s="44"/>
       <c r="S28" s="10"/>
-      <c r="T28" s="73"/>
-      <c r="U28" s="73"/>
+      <c r="T28" s="70"/>
+      <c r="U28" s="70"/>
       <c r="V28" s="44"/>
       <c r="W28" s="44"/>
       <c r="X28" s="44"/>
@@ -4329,7 +4257,7 @@
       <c r="AH28" s="40"/>
       <c r="AI28" s="10"/>
       <c r="AJ28" s="44" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="AK28" s="44"/>
       <c r="AL28" s="44"/>
@@ -4345,7 +4273,7 @@
       <c r="AV28" s="44"/>
       <c r="AW28" s="40"/>
       <c r="AX28" s="14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AY28" s="46"/>
       <c r="AZ28" s="44"/>
@@ -4358,7 +4286,7 @@
       <c r="BG28" s="44"/>
       <c r="BH28" s="44"/>
       <c r="BI28" s="44"/>
-      <c r="BJ28" s="44"/>
+      <c r="BJ28" s="40"/>
       <c r="BK28" s="10"/>
       <c r="BL28" s="44"/>
       <c r="BM28" s="40"/>
@@ -4378,7 +4306,7 @@
       <c r="C29" s="42"/>
       <c r="D29" s="6"/>
       <c r="E29" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F29" s="44"/>
       <c r="G29" s="44"/>
@@ -4394,8 +4322,8 @@
       <c r="Q29" s="44"/>
       <c r="R29" s="44"/>
       <c r="S29" s="10"/>
-      <c r="T29" s="73"/>
-      <c r="U29" s="73"/>
+      <c r="T29" s="70"/>
+      <c r="U29" s="70"/>
       <c r="V29" s="44"/>
       <c r="W29" s="44"/>
       <c r="X29" s="44"/>
@@ -4436,7 +4364,7 @@
       <c r="BG29" s="44"/>
       <c r="BH29" s="44"/>
       <c r="BI29" s="44"/>
-      <c r="BJ29" s="44"/>
+      <c r="BJ29" s="40"/>
       <c r="BK29" s="10"/>
       <c r="BL29" s="44"/>
       <c r="BM29" s="40"/>
@@ -4456,7 +4384,7 @@
       <c r="C30" s="42"/>
       <c r="D30" s="6"/>
       <c r="E30" s="10" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F30" s="44"/>
       <c r="G30" s="44"/>
@@ -4488,7 +4416,7 @@
       <c r="AG30" s="44"/>
       <c r="AH30" s="40"/>
       <c r="AI30" s="10" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AJ30" s="44"/>
       <c r="AK30" s="44"/>
@@ -4505,7 +4433,7 @@
       <c r="AV30" s="44"/>
       <c r="AW30" s="40"/>
       <c r="AX30" s="14" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AY30" s="46"/>
       <c r="AZ30" s="44"/>
@@ -4518,7 +4446,7 @@
       <c r="BG30" s="44"/>
       <c r="BH30" s="44"/>
       <c r="BI30" s="44"/>
-      <c r="BJ30" s="44"/>
+      <c r="BJ30" s="40"/>
       <c r="BK30" s="10"/>
       <c r="BL30" s="44"/>
       <c r="BM30" s="40"/>
@@ -4537,7 +4465,9 @@
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="10"/>
+      <c r="E31" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="F31" s="44"/>
       <c r="G31" s="44"/>
       <c r="H31" s="44"/>
@@ -4568,7 +4498,7 @@
       <c r="AG31" s="44"/>
       <c r="AH31" s="40"/>
       <c r="AI31" s="10" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AJ31" s="44"/>
       <c r="AK31" s="44"/>
@@ -4585,7 +4515,7 @@
       <c r="AV31" s="44"/>
       <c r="AW31" s="40"/>
       <c r="AX31" s="14" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AY31" s="46"/>
       <c r="AZ31" s="44"/>
@@ -4598,7 +4528,7 @@
       <c r="BG31" s="44"/>
       <c r="BH31" s="44"/>
       <c r="BI31" s="44"/>
-      <c r="BJ31" s="44"/>
+      <c r="BJ31" s="40"/>
       <c r="BK31" s="10"/>
       <c r="BL31" s="44"/>
       <c r="BM31" s="40"/>
@@ -4663,7 +4593,7 @@
       <c r="AV32" s="44"/>
       <c r="AW32" s="40"/>
       <c r="AX32" s="14" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AY32" s="46"/>
       <c r="AZ32" s="44"/>
@@ -4676,7 +4606,7 @@
       <c r="BG32" s="44"/>
       <c r="BH32" s="44"/>
       <c r="BI32" s="44"/>
-      <c r="BJ32" s="44"/>
+      <c r="BJ32" s="40"/>
       <c r="BK32" s="10"/>
       <c r="BL32" s="44"/>
       <c r="BM32" s="40"/>
@@ -4741,7 +4671,7 @@
       <c r="AV33" s="44"/>
       <c r="AW33" s="40"/>
       <c r="AX33" s="14" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AY33" s="46"/>
       <c r="AZ33" s="44"/>
@@ -4754,7 +4684,7 @@
       <c r="BG33" s="44"/>
       <c r="BH33" s="44"/>
       <c r="BI33" s="44"/>
-      <c r="BJ33" s="44"/>
+      <c r="BJ33" s="40"/>
       <c r="BK33" s="10"/>
       <c r="BL33" s="44"/>
       <c r="BM33" s="40"/>
@@ -4830,7 +4760,7 @@
       <c r="BG34" s="43"/>
       <c r="BH34" s="46"/>
       <c r="BI34" s="46"/>
-      <c r="BJ34" s="46"/>
+      <c r="BJ34" s="13"/>
       <c r="BK34" s="14"/>
       <c r="BL34" s="46"/>
       <c r="BM34" s="13"/>
@@ -4906,7 +4836,7 @@
       <c r="BG35" s="43"/>
       <c r="BH35" s="46"/>
       <c r="BI35" s="46"/>
-      <c r="BJ35" s="46"/>
+      <c r="BJ35" s="13"/>
       <c r="BK35" s="14"/>
       <c r="BL35" s="46"/>
       <c r="BM35" s="13"/>
@@ -4921,199 +4851,183 @@
       <c r="BV35" s="11"/>
     </row>
     <row r="36" spans="1:74" ht="14.4" customHeight="1">
-      <c r="A36" s="52"/>
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="21"/>
-      <c r="V36" s="21"/>
-      <c r="W36" s="21"/>
-      <c r="X36" s="21"/>
-      <c r="Y36" s="19"/>
-      <c r="Z36" s="19"/>
-      <c r="AA36" s="19"/>
-      <c r="AB36" s="19"/>
-      <c r="AC36" s="19"/>
-      <c r="AD36" s="19"/>
-      <c r="AE36" s="19"/>
-      <c r="AF36" s="19"/>
-      <c r="AG36" s="19"/>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="23" t="s">
-        <v>62</v>
+      <c r="A36" s="5"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="45"/>
+      <c r="V36" s="45"/>
+      <c r="W36" s="45"/>
+      <c r="X36" s="45"/>
+      <c r="Y36" s="43"/>
+      <c r="Z36" s="43"/>
+      <c r="AA36" s="43"/>
+      <c r="AB36" s="43"/>
+      <c r="AC36" s="43"/>
+      <c r="AD36" s="43"/>
+      <c r="AE36" s="43"/>
+      <c r="AF36" s="43"/>
+      <c r="AG36" s="43"/>
+      <c r="AH36" s="13"/>
+      <c r="AI36" s="14" t="s">
+        <v>54</v>
       </c>
-      <c r="AJ36" s="24"/>
-      <c r="AK36" s="24"/>
-      <c r="AL36" s="24"/>
-      <c r="AM36" s="24"/>
-      <c r="AN36" s="24"/>
-      <c r="AO36" s="24"/>
-      <c r="AP36" s="24"/>
-      <c r="AQ36" s="19"/>
-      <c r="AR36" s="19"/>
-      <c r="AS36" s="19"/>
-      <c r="AT36" s="19"/>
-      <c r="AU36" s="19"/>
-      <c r="AV36" s="19"/>
-      <c r="AW36" s="20"/>
-      <c r="AX36" s="23" t="s">
-        <v>63</v>
+      <c r="AJ36" s="46"/>
+      <c r="AK36" s="46"/>
+      <c r="AL36" s="46"/>
+      <c r="AM36" s="46"/>
+      <c r="AN36" s="46"/>
+      <c r="AO36" s="46"/>
+      <c r="AP36" s="46"/>
+      <c r="AQ36" s="43"/>
+      <c r="AR36" s="43"/>
+      <c r="AS36" s="43"/>
+      <c r="AT36" s="43"/>
+      <c r="AU36" s="43"/>
+      <c r="AV36" s="43"/>
+      <c r="AW36" s="9"/>
+      <c r="AX36" s="10" t="s">
+        <v>75</v>
       </c>
-      <c r="AY36" s="24"/>
-      <c r="AZ36" s="24"/>
-      <c r="BA36" s="24"/>
-      <c r="BB36" s="24"/>
-      <c r="BC36" s="24"/>
-      <c r="BD36" s="24"/>
-      <c r="BE36" s="24"/>
-      <c r="BF36" s="19"/>
-      <c r="BG36" s="19"/>
-      <c r="BH36" s="24"/>
-      <c r="BI36" s="24"/>
-      <c r="BJ36" s="24"/>
-      <c r="BK36" s="23"/>
-      <c r="BL36" s="24"/>
-      <c r="BM36" s="22"/>
-      <c r="BN36" s="23"/>
-      <c r="BO36" s="24"/>
-      <c r="BP36" s="24"/>
-      <c r="BQ36" s="22"/>
-      <c r="BR36" s="23"/>
-      <c r="BS36" s="24"/>
-      <c r="BT36" s="24"/>
-      <c r="BU36" s="22"/>
+      <c r="AY36" s="46"/>
+      <c r="AZ36" s="46"/>
+      <c r="BA36" s="46"/>
+      <c r="BB36" s="46"/>
+      <c r="BC36" s="46"/>
+      <c r="BD36" s="46"/>
+      <c r="BE36" s="46"/>
+      <c r="BF36" s="43"/>
+      <c r="BG36" s="43"/>
+      <c r="BH36" s="46"/>
+      <c r="BI36" s="46"/>
+      <c r="BJ36" s="13"/>
+      <c r="BK36" s="14"/>
+      <c r="BL36" s="46"/>
+      <c r="BM36" s="13"/>
+      <c r="BN36" s="14"/>
+      <c r="BO36" s="46"/>
+      <c r="BP36" s="46"/>
+      <c r="BQ36" s="13"/>
+      <c r="BR36" s="14"/>
+      <c r="BS36" s="46"/>
+      <c r="BT36" s="46"/>
+      <c r="BU36" s="13"/>
       <c r="BV36" s="11"/>
     </row>
     <row r="37" spans="1:74" ht="14.4" customHeight="1">
-      <c r="A37" s="25">
-        <v>5</v>
-      </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="72"/>
-      <c r="L37" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="M37" s="32"/>
-      <c r="N37" s="32"/>
-      <c r="O37" s="32"/>
-      <c r="P37" s="32"/>
-      <c r="Q37" s="32"/>
-      <c r="R37" s="32"/>
-      <c r="S37" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="T37" s="74"/>
-      <c r="U37" s="74"/>
-      <c r="V37" s="32"/>
-      <c r="W37" s="32"/>
-      <c r="X37" s="32"/>
-      <c r="Y37" s="32"/>
-      <c r="Z37" s="32"/>
-      <c r="AA37" s="32"/>
-      <c r="AB37" s="32"/>
-      <c r="AC37" s="32"/>
-      <c r="AD37" s="32"/>
-      <c r="AE37" s="32"/>
-      <c r="AF37" s="32"/>
-      <c r="AG37" s="32"/>
-      <c r="AH37" s="72"/>
-      <c r="AI37" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ37" s="44"/>
-      <c r="AK37" s="32"/>
-      <c r="AL37" s="32"/>
-      <c r="AM37" s="32"/>
-      <c r="AN37" s="32"/>
-      <c r="AO37" s="32"/>
-      <c r="AP37" s="32"/>
-      <c r="AQ37" s="32"/>
-      <c r="AR37" s="32"/>
-      <c r="AS37" s="32"/>
-      <c r="AT37" s="32"/>
-      <c r="AU37" s="32"/>
-      <c r="AV37" s="32"/>
-      <c r="AW37" s="72"/>
-      <c r="AX37" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="AY37" s="35"/>
-      <c r="AZ37" s="32"/>
-      <c r="BA37" s="32"/>
-      <c r="BB37" s="32"/>
-      <c r="BC37" s="32"/>
-      <c r="BD37" s="32"/>
-      <c r="BE37" s="32"/>
-      <c r="BF37" s="32"/>
-      <c r="BG37" s="32"/>
-      <c r="BH37" s="32"/>
-      <c r="BI37" s="32"/>
-      <c r="BJ37" s="32"/>
-      <c r="BK37" s="31"/>
-      <c r="BL37" s="32"/>
-      <c r="BM37" s="72"/>
-      <c r="BN37" s="31"/>
-      <c r="BO37" s="32"/>
-      <c r="BP37" s="32"/>
-      <c r="BQ37" s="72"/>
-      <c r="BR37" s="31"/>
-      <c r="BS37" s="32"/>
-      <c r="BT37" s="32"/>
-      <c r="BU37" s="72"/>
+      <c r="A37" s="5"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="43"/>
+      <c r="R37" s="43"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="45"/>
+      <c r="V37" s="45"/>
+      <c r="W37" s="45"/>
+      <c r="X37" s="45"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="43"/>
+      <c r="AE37" s="43"/>
+      <c r="AF37" s="43"/>
+      <c r="AG37" s="43"/>
+      <c r="AH37" s="13"/>
+      <c r="AI37" s="14"/>
+      <c r="AJ37" s="46"/>
+      <c r="AK37" s="46"/>
+      <c r="AL37" s="46"/>
+      <c r="AM37" s="46"/>
+      <c r="AN37" s="46"/>
+      <c r="AO37" s="46"/>
+      <c r="AP37" s="46"/>
+      <c r="AQ37" s="43"/>
+      <c r="AR37" s="43"/>
+      <c r="AS37" s="43"/>
+      <c r="AT37" s="43"/>
+      <c r="AU37" s="43"/>
+      <c r="AV37" s="43"/>
+      <c r="AW37" s="9"/>
+      <c r="AX37" s="125"/>
+      <c r="AY37" s="46"/>
+      <c r="AZ37" s="46"/>
+      <c r="BA37" s="46"/>
+      <c r="BB37" s="46"/>
+      <c r="BC37" s="46"/>
+      <c r="BD37" s="46"/>
+      <c r="BE37" s="46"/>
+      <c r="BF37" s="43"/>
+      <c r="BG37" s="43"/>
+      <c r="BH37" s="46"/>
+      <c r="BI37" s="46"/>
+      <c r="BJ37" s="46"/>
+      <c r="BK37" s="14"/>
+      <c r="BL37" s="46"/>
+      <c r="BM37" s="13"/>
+      <c r="BN37" s="14"/>
+      <c r="BO37" s="46"/>
+      <c r="BP37" s="46"/>
+      <c r="BQ37" s="13"/>
+      <c r="BR37" s="14"/>
+      <c r="BS37" s="46"/>
+      <c r="BT37" s="46"/>
+      <c r="BU37" s="13"/>
       <c r="BV37" s="11"/>
     </row>
     <row r="38" spans="1:74" ht="14.4" customHeight="1">
       <c r="A38" s="5"/>
       <c r="B38" s="42"/>
       <c r="C38" s="42"/>
-      <c r="D38" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="7"/>
       <c r="F38" s="44"/>
       <c r="G38" s="44"/>
       <c r="H38" s="44"/>
       <c r="I38" s="44"/>
       <c r="J38" s="44"/>
       <c r="K38" s="40"/>
-      <c r="L38" s="10"/>
+      <c r="L38" s="7"/>
       <c r="M38" s="44"/>
       <c r="N38" s="44"/>
       <c r="O38" s="44"/>
       <c r="P38" s="44"/>
       <c r="Q38" s="44"/>
       <c r="R38" s="44"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="73"/>
-      <c r="U38" s="73"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="70"/>
+      <c r="U38" s="70"/>
       <c r="V38" s="44"/>
       <c r="W38" s="44"/>
       <c r="X38" s="44"/>
@@ -5128,7 +5042,7 @@
       <c r="AG38" s="44"/>
       <c r="AH38" s="40"/>
       <c r="AI38" s="10" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="AJ38" s="44"/>
       <c r="AK38" s="44"/>
@@ -5145,7 +5059,7 @@
       <c r="AV38" s="44"/>
       <c r="AW38" s="40"/>
       <c r="AX38" s="14" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AY38" s="46"/>
       <c r="AZ38" s="44"/>
@@ -5176,10 +5090,10 @@
       <c r="A39" s="5"/>
       <c r="B39" s="42"/>
       <c r="C39" s="42"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="10" t="s">
-        <v>35</v>
+      <c r="D39" s="6" t="s">
+        <v>31</v>
       </c>
+      <c r="E39" s="10"/>
       <c r="F39" s="44"/>
       <c r="G39" s="44"/>
       <c r="H39" s="44"/>
@@ -5193,9 +5107,9 @@
       <c r="P39" s="44"/>
       <c r="Q39" s="44"/>
       <c r="R39" s="44"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="73"/>
-      <c r="U39" s="73"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="70"/>
+      <c r="U39" s="70"/>
       <c r="V39" s="44"/>
       <c r="W39" s="44"/>
       <c r="X39" s="44"/>
@@ -5209,7 +5123,9 @@
       <c r="AF39" s="44"/>
       <c r="AG39" s="44"/>
       <c r="AH39" s="40"/>
-      <c r="AI39" s="10"/>
+      <c r="AI39" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="AJ39" s="44"/>
       <c r="AK39" s="44"/>
       <c r="AL39" s="44"/>
@@ -5224,10 +5140,10 @@
       <c r="AU39" s="44"/>
       <c r="AV39" s="44"/>
       <c r="AW39" s="40"/>
-      <c r="AX39" s="14"/>
-      <c r="AY39" s="46" t="s">
-        <v>68</v>
+      <c r="AX39" s="14" t="s">
+        <v>56</v>
       </c>
+      <c r="AY39" s="46"/>
       <c r="AZ39" s="44"/>
       <c r="BA39" s="44"/>
       <c r="BB39" s="44"/>
@@ -5257,9 +5173,7 @@
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
       <c r="D40" s="6"/>
-      <c r="E40" s="10" t="s">
-        <v>80</v>
-      </c>
+      <c r="E40" s="10"/>
       <c r="F40" s="44"/>
       <c r="G40" s="44"/>
       <c r="H40" s="44"/>
@@ -5273,9 +5187,9 @@
       <c r="P40" s="44"/>
       <c r="Q40" s="44"/>
       <c r="R40" s="44"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="44"/>
-      <c r="U40" s="44"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="70"/>
+      <c r="U40" s="70"/>
       <c r="V40" s="44"/>
       <c r="W40" s="44"/>
       <c r="X40" s="44"/>
@@ -5306,7 +5220,7 @@
       <c r="AW40" s="40"/>
       <c r="AX40" s="14"/>
       <c r="AY40" s="46" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="AZ40" s="44"/>
       <c r="BA40" s="44"/>
@@ -5337,12 +5251,6 @@
       <c r="B41" s="42"/>
       <c r="C41" s="42"/>
       <c r="D41" s="6"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="44"/>
       <c r="K41" s="40"/>
       <c r="L41" s="10"/>
       <c r="M41" s="44"/>
@@ -5384,7 +5292,7 @@
       <c r="AW41" s="40"/>
       <c r="AX41" s="14"/>
       <c r="AY41" s="46" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="AZ41" s="44"/>
       <c r="BA41" s="44"/>
@@ -5462,7 +5370,7 @@
       <c r="AW42" s="40"/>
       <c r="AX42" s="14"/>
       <c r="AY42" s="46" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="AZ42" s="44"/>
       <c r="BA42" s="44"/>
@@ -5538,10 +5446,10 @@
       <c r="AU43" s="44"/>
       <c r="AV43" s="44"/>
       <c r="AW43" s="40"/>
-      <c r="AX43" s="14" t="s">
-        <v>72</v>
+      <c r="AX43" s="14"/>
+      <c r="AY43" s="46" t="s">
+        <v>60</v>
       </c>
-      <c r="AY43" s="46"/>
       <c r="AZ43" s="44"/>
       <c r="BA43" s="44"/>
       <c r="BB43" s="44"/>
@@ -5571,77 +5479,77 @@
       <c r="B44" s="42"/>
       <c r="C44" s="42"/>
       <c r="D44" s="6"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="43"/>
-      <c r="N44" s="43"/>
-      <c r="O44" s="43"/>
-      <c r="P44" s="43"/>
-      <c r="Q44" s="43"/>
-      <c r="R44" s="43"/>
-      <c r="S44" s="7"/>
-      <c r="T44" s="43"/>
-      <c r="U44" s="45"/>
-      <c r="V44" s="45"/>
-      <c r="W44" s="45"/>
-      <c r="X44" s="45"/>
-      <c r="Y44" s="43"/>
-      <c r="Z44" s="43"/>
-      <c r="AA44" s="43"/>
-      <c r="AB44" s="43"/>
-      <c r="AC44" s="43"/>
-      <c r="AD44" s="43"/>
-      <c r="AE44" s="43"/>
-      <c r="AF44" s="43"/>
-      <c r="AG44" s="43"/>
-      <c r="AH44" s="13"/>
-      <c r="AI44" s="14"/>
-      <c r="AJ44" s="46"/>
-      <c r="AK44" s="46"/>
-      <c r="AL44" s="46"/>
-      <c r="AM44" s="46"/>
-      <c r="AN44" s="46"/>
-      <c r="AO44" s="46"/>
-      <c r="AP44" s="46"/>
-      <c r="AQ44" s="43"/>
-      <c r="AR44" s="43"/>
-      <c r="AS44" s="43"/>
-      <c r="AT44" s="43"/>
-      <c r="AU44" s="43"/>
-      <c r="AV44" s="43"/>
-      <c r="AW44" s="9"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="44"/>
+      <c r="N44" s="44"/>
+      <c r="O44" s="44"/>
+      <c r="P44" s="44"/>
+      <c r="Q44" s="44"/>
+      <c r="R44" s="44"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="44"/>
+      <c r="U44" s="44"/>
+      <c r="V44" s="44"/>
+      <c r="W44" s="44"/>
+      <c r="X44" s="44"/>
+      <c r="Y44" s="44"/>
+      <c r="Z44" s="44"/>
+      <c r="AA44" s="44"/>
+      <c r="AB44" s="44"/>
+      <c r="AC44" s="44"/>
+      <c r="AD44" s="44"/>
+      <c r="AE44" s="44"/>
+      <c r="AF44" s="44"/>
+      <c r="AG44" s="44"/>
+      <c r="AH44" s="40"/>
+      <c r="AI44" s="10"/>
+      <c r="AJ44" s="44"/>
+      <c r="AK44" s="44"/>
+      <c r="AL44" s="44"/>
+      <c r="AM44" s="44"/>
+      <c r="AN44" s="44"/>
+      <c r="AO44" s="44"/>
+      <c r="AP44" s="44"/>
+      <c r="AQ44" s="44"/>
+      <c r="AR44" s="44"/>
+      <c r="AS44" s="44"/>
+      <c r="AT44" s="44"/>
+      <c r="AU44" s="44"/>
+      <c r="AV44" s="44"/>
+      <c r="AW44" s="40"/>
       <c r="AX44" s="14" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="AY44" s="46"/>
-      <c r="AZ44" s="46"/>
-      <c r="BA44" s="46"/>
-      <c r="BB44" s="46"/>
-      <c r="BC44" s="46"/>
-      <c r="BD44" s="46"/>
-      <c r="BE44" s="46"/>
-      <c r="BF44" s="43"/>
-      <c r="BG44" s="43"/>
-      <c r="BH44" s="46"/>
-      <c r="BI44" s="46"/>
-      <c r="BJ44" s="46"/>
-      <c r="BK44" s="14"/>
-      <c r="BL44" s="46"/>
-      <c r="BM44" s="13"/>
-      <c r="BN44" s="14"/>
-      <c r="BO44" s="46"/>
-      <c r="BP44" s="46"/>
-      <c r="BQ44" s="13"/>
-      <c r="BR44" s="14"/>
-      <c r="BS44" s="46"/>
-      <c r="BT44" s="46"/>
-      <c r="BU44" s="13"/>
+      <c r="AZ44" s="44"/>
+      <c r="BA44" s="44"/>
+      <c r="BB44" s="44"/>
+      <c r="BC44" s="44"/>
+      <c r="BD44" s="44"/>
+      <c r="BE44" s="44"/>
+      <c r="BF44" s="44"/>
+      <c r="BG44" s="44"/>
+      <c r="BH44" s="44"/>
+      <c r="BI44" s="44"/>
+      <c r="BJ44" s="44"/>
+      <c r="BK44" s="10"/>
+      <c r="BL44" s="44"/>
+      <c r="BM44" s="40"/>
+      <c r="BN44" s="10"/>
+      <c r="BO44" s="44"/>
+      <c r="BP44" s="44"/>
+      <c r="BQ44" s="40"/>
+      <c r="BR44" s="10"/>
+      <c r="BS44" s="44"/>
+      <c r="BT44" s="44"/>
+      <c r="BU44" s="40"/>
       <c r="BV44" s="11"/>
     </row>
     <row r="45" spans="1:74" ht="14.4" customHeight="1">
@@ -5694,7 +5602,9 @@
       <c r="AU45" s="43"/>
       <c r="AV45" s="43"/>
       <c r="AW45" s="9"/>
-      <c r="AX45" s="14"/>
+      <c r="AX45" s="14" t="s">
+        <v>65</v>
+      </c>
       <c r="AY45" s="46"/>
       <c r="AZ45" s="46"/>
       <c r="BA45" s="46"/>
@@ -5755,9 +5665,7 @@
       <c r="AF46" s="43"/>
       <c r="AG46" s="43"/>
       <c r="AH46" s="13"/>
-      <c r="AI46" s="14" t="s">
-        <v>74</v>
-      </c>
+      <c r="AI46" s="14"/>
       <c r="AJ46" s="46"/>
       <c r="AK46" s="46"/>
       <c r="AL46" s="46"/>
@@ -5772,9 +5680,7 @@
       <c r="AU46" s="43"/>
       <c r="AV46" s="43"/>
       <c r="AW46" s="9"/>
-      <c r="AX46" s="14" t="s">
-        <v>73</v>
-      </c>
+      <c r="AX46" s="14"/>
       <c r="AY46" s="46"/>
       <c r="AZ46" s="46"/>
       <c r="BA46" s="46"/>
@@ -5835,7 +5741,9 @@
       <c r="AF47" s="43"/>
       <c r="AG47" s="43"/>
       <c r="AH47" s="13"/>
-      <c r="AI47" s="14"/>
+      <c r="AI47" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="AJ47" s="46"/>
       <c r="AK47" s="46"/>
       <c r="AL47" s="46"/>
@@ -5850,7 +5758,9 @@
       <c r="AU47" s="43"/>
       <c r="AV47" s="43"/>
       <c r="AW47" s="9"/>
-      <c r="AX47" s="14"/>
+      <c r="AX47" s="14" t="s">
+        <v>62</v>
+      </c>
       <c r="AY47" s="46"/>
       <c r="AZ47" s="46"/>
       <c r="BA47" s="46"/>
@@ -5911,9 +5821,7 @@
       <c r="AF48" s="43"/>
       <c r="AG48" s="43"/>
       <c r="AH48" s="13"/>
-      <c r="AI48" s="14" t="s">
-        <v>75</v>
-      </c>
+      <c r="AI48" s="14"/>
       <c r="AJ48" s="46"/>
       <c r="AK48" s="46"/>
       <c r="AL48" s="46"/>
@@ -5928,9 +5836,7 @@
       <c r="AU48" s="43"/>
       <c r="AV48" s="43"/>
       <c r="AW48" s="9"/>
-      <c r="AX48" s="14" t="s">
-        <v>76</v>
-      </c>
+      <c r="AX48" s="14"/>
       <c r="AY48" s="46"/>
       <c r="AZ48" s="46"/>
       <c r="BA48" s="46"/>
@@ -5991,7 +5897,9 @@
       <c r="AF49" s="43"/>
       <c r="AG49" s="43"/>
       <c r="AH49" s="13"/>
-      <c r="AI49" s="14"/>
+      <c r="AI49" s="14" t="s">
+        <v>73</v>
+      </c>
       <c r="AJ49" s="46"/>
       <c r="AK49" s="46"/>
       <c r="AL49" s="46"/>
@@ -6006,7 +5914,9 @@
       <c r="AU49" s="43"/>
       <c r="AV49" s="43"/>
       <c r="AW49" s="9"/>
-      <c r="AX49" s="14"/>
+      <c r="AX49" s="14" t="s">
+        <v>63</v>
+      </c>
       <c r="AY49" s="46"/>
       <c r="AZ49" s="46"/>
       <c r="BA49" s="46"/>
@@ -6067,9 +5977,7 @@
       <c r="AF50" s="43"/>
       <c r="AG50" s="43"/>
       <c r="AH50" s="13"/>
-      <c r="AI50" s="14" t="s">
-        <v>77</v>
-      </c>
+      <c r="AI50" s="14"/>
       <c r="AJ50" s="46"/>
       <c r="AK50" s="46"/>
       <c r="AL50" s="46"/>
@@ -6084,9 +5992,7 @@
       <c r="AU50" s="43"/>
       <c r="AV50" s="43"/>
       <c r="AW50" s="9"/>
-      <c r="AX50" s="14" t="s">
-        <v>78</v>
-      </c>
+      <c r="AX50" s="14"/>
       <c r="AY50" s="46"/>
       <c r="AZ50" s="46"/>
       <c r="BA50" s="46"/>
@@ -6147,7 +6053,9 @@
       <c r="AF51" s="43"/>
       <c r="AG51" s="43"/>
       <c r="AH51" s="13"/>
-      <c r="AI51" s="14"/>
+      <c r="AI51" s="14" t="s">
+        <v>74</v>
+      </c>
       <c r="AJ51" s="46"/>
       <c r="AK51" s="46"/>
       <c r="AL51" s="46"/>
@@ -6162,7 +6070,9 @@
       <c r="AU51" s="43"/>
       <c r="AV51" s="43"/>
       <c r="AW51" s="9"/>
-      <c r="AX51" s="14"/>
+      <c r="AX51" s="14" t="s">
+        <v>64</v>
+      </c>
       <c r="AY51" s="46"/>
       <c r="AZ51" s="46"/>
       <c r="BA51" s="46"/>
@@ -6189,85 +6099,80 @@
       <c r="BV51" s="11"/>
     </row>
     <row r="52" spans="1:79" ht="14.4" customHeight="1">
-      <c r="A52" s="41"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="8"/>
-      <c r="M52" s="8"/>
-      <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="8"/>
-      <c r="S52" s="8"/>
-      <c r="T52" s="8"/>
-      <c r="U52" s="8"/>
-      <c r="V52" s="8"/>
-      <c r="W52" s="8"/>
-      <c r="X52" s="8"/>
-      <c r="Y52" s="8"/>
-      <c r="Z52" s="8"/>
-      <c r="AA52" s="8"/>
-      <c r="AB52" s="8"/>
-      <c r="AC52" s="12"/>
-      <c r="AD52" s="12"/>
-      <c r="AE52" s="12"/>
-      <c r="AF52" s="12"/>
-      <c r="AG52" s="8"/>
-      <c r="AH52" s="8"/>
-      <c r="AI52" s="8"/>
-      <c r="AJ52" s="8"/>
-      <c r="AK52" s="8"/>
-      <c r="AL52" s="8"/>
-      <c r="AM52" s="8"/>
-      <c r="AN52" s="15"/>
-      <c r="AO52" s="15"/>
-      <c r="AP52" s="15"/>
-      <c r="AQ52" s="15"/>
-      <c r="AR52" s="15"/>
-      <c r="AS52" s="15"/>
-      <c r="AT52" s="15"/>
-      <c r="AU52" s="15"/>
-      <c r="AV52" s="15"/>
-      <c r="AW52" s="8"/>
-      <c r="AX52" s="8"/>
-      <c r="AY52" s="8"/>
-      <c r="AZ52" s="8"/>
-      <c r="BA52" s="15"/>
-      <c r="BB52" s="15"/>
-      <c r="BC52" s="15"/>
-      <c r="BD52" s="15"/>
-      <c r="BE52" s="15"/>
-      <c r="BF52" s="15"/>
-      <c r="BG52" s="15"/>
-      <c r="BH52" s="15"/>
-      <c r="BI52" s="8"/>
-      <c r="BJ52" s="8"/>
-      <c r="BK52" s="8"/>
-      <c r="BL52" s="8"/>
-      <c r="BM52" s="15"/>
-      <c r="BN52" s="15"/>
-      <c r="BO52" s="15"/>
-      <c r="BP52" s="15"/>
-      <c r="BQ52" s="15"/>
-      <c r="BR52" s="15"/>
-      <c r="BS52" s="15"/>
-      <c r="BT52" s="15"/>
-      <c r="BU52" s="15"/>
-      <c r="BV52" s="15"/>
-      <c r="BW52" s="11"/>
-      <c r="BX52" s="11"/>
-      <c r="BY52" s="11"/>
-      <c r="BZ52" s="11"/>
-      <c r="CA52" s="11"/>
+      <c r="A52" s="52"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="19"/>
+      <c r="U52" s="21"/>
+      <c r="V52" s="21"/>
+      <c r="W52" s="21"/>
+      <c r="X52" s="21"/>
+      <c r="Y52" s="19"/>
+      <c r="Z52" s="19"/>
+      <c r="AA52" s="19"/>
+      <c r="AB52" s="19"/>
+      <c r="AC52" s="19"/>
+      <c r="AD52" s="19"/>
+      <c r="AE52" s="19"/>
+      <c r="AF52" s="19"/>
+      <c r="AG52" s="19"/>
+      <c r="AH52" s="22"/>
+      <c r="AI52" s="90"/>
+      <c r="AJ52" s="65"/>
+      <c r="AK52" s="65"/>
+      <c r="AL52" s="65"/>
+      <c r="AM52" s="65"/>
+      <c r="AN52" s="65"/>
+      <c r="AO52" s="65"/>
+      <c r="AP52" s="65"/>
+      <c r="AQ52" s="65"/>
+      <c r="AR52" s="65"/>
+      <c r="AS52" s="65"/>
+      <c r="AT52" s="65"/>
+      <c r="AU52" s="65"/>
+      <c r="AV52" s="65"/>
+      <c r="AW52" s="91"/>
+      <c r="AX52" s="23"/>
+      <c r="AY52" s="24"/>
+      <c r="AZ52" s="24"/>
+      <c r="BA52" s="24"/>
+      <c r="BB52" s="24"/>
+      <c r="BC52" s="24"/>
+      <c r="BD52" s="24"/>
+      <c r="BE52" s="24"/>
+      <c r="BF52" s="19"/>
+      <c r="BG52" s="19"/>
+      <c r="BH52" s="24"/>
+      <c r="BI52" s="24"/>
+      <c r="BJ52" s="24"/>
+      <c r="BK52" s="23"/>
+      <c r="BL52" s="24"/>
+      <c r="BM52" s="22"/>
+      <c r="BN52" s="23"/>
+      <c r="BO52" s="24"/>
+      <c r="BP52" s="24"/>
+      <c r="BQ52" s="22"/>
+      <c r="BR52" s="23"/>
+      <c r="BS52" s="24"/>
+      <c r="BT52" s="24"/>
+      <c r="BU52" s="22"/>
+      <c r="BV52" s="11"/>
     </row>
     <row r="53" spans="1:79" ht="14.4" customHeight="1">
       <c r="A53" s="41"/>
@@ -31703,8 +31608,89 @@
       <c r="BZ366" s="11"/>
       <c r="CA366" s="11"/>
     </row>
+    <row r="367" spans="1:79" ht="14.4" customHeight="1">
+      <c r="A367" s="41"/>
+      <c r="B367" s="8"/>
+      <c r="C367" s="8"/>
+      <c r="D367" s="8"/>
+      <c r="E367" s="8"/>
+      <c r="F367" s="8"/>
+      <c r="G367" s="8"/>
+      <c r="H367" s="8"/>
+      <c r="I367" s="8"/>
+      <c r="J367" s="8"/>
+      <c r="K367" s="8"/>
+      <c r="L367" s="8"/>
+      <c r="M367" s="8"/>
+      <c r="N367" s="8"/>
+      <c r="O367" s="8"/>
+      <c r="P367" s="8"/>
+      <c r="Q367" s="8"/>
+      <c r="R367" s="8"/>
+      <c r="S367" s="8"/>
+      <c r="T367" s="8"/>
+      <c r="U367" s="8"/>
+      <c r="V367" s="8"/>
+      <c r="W367" s="8"/>
+      <c r="X367" s="8"/>
+      <c r="Y367" s="8"/>
+      <c r="Z367" s="8"/>
+      <c r="AA367" s="8"/>
+      <c r="AB367" s="8"/>
+      <c r="AC367" s="12"/>
+      <c r="AD367" s="12"/>
+      <c r="AE367" s="12"/>
+      <c r="AF367" s="12"/>
+      <c r="AG367" s="8"/>
+      <c r="AH367" s="8"/>
+      <c r="AI367" s="8"/>
+      <c r="AJ367" s="8"/>
+      <c r="AK367" s="8"/>
+      <c r="AL367" s="8"/>
+      <c r="AM367" s="8"/>
+      <c r="AN367" s="15"/>
+      <c r="AO367" s="15"/>
+      <c r="AP367" s="15"/>
+      <c r="AQ367" s="15"/>
+      <c r="AR367" s="15"/>
+      <c r="AS367" s="15"/>
+      <c r="AT367" s="15"/>
+      <c r="AU367" s="15"/>
+      <c r="AV367" s="15"/>
+      <c r="AW367" s="8"/>
+      <c r="AX367" s="8"/>
+      <c r="AY367" s="8"/>
+      <c r="AZ367" s="8"/>
+      <c r="BA367" s="15"/>
+      <c r="BB367" s="15"/>
+      <c r="BC367" s="15"/>
+      <c r="BD367" s="15"/>
+      <c r="BE367" s="15"/>
+      <c r="BF367" s="15"/>
+      <c r="BG367" s="15"/>
+      <c r="BH367" s="15"/>
+      <c r="BI367" s="8"/>
+      <c r="BJ367" s="8"/>
+      <c r="BK367" s="8"/>
+      <c r="BL367" s="8"/>
+      <c r="BM367" s="15"/>
+      <c r="BN367" s="15"/>
+      <c r="BO367" s="15"/>
+      <c r="BP367" s="15"/>
+      <c r="BQ367" s="15"/>
+      <c r="BR367" s="15"/>
+      <c r="BS367" s="15"/>
+      <c r="BT367" s="15"/>
+      <c r="BU367" s="15"/>
+      <c r="BV367" s="15"/>
+      <c r="BW367" s="11"/>
+      <c r="BX367" s="11"/>
+      <c r="BY367" s="11"/>
+      <c r="BZ367" s="11"/>
+      <c r="CA367" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="AI5:AW6"/>
     <mergeCell ref="AX5:BJ6"/>
     <mergeCell ref="A1:T2"/>
@@ -31716,6 +31702,7 @@
     <mergeCell ref="Y1:AH1"/>
     <mergeCell ref="Y2:AH2"/>
     <mergeCell ref="AY1:BB2"/>
+    <mergeCell ref="A5:D6"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.39370078740157483" footer="0.39370078740157483"/>
